--- a/Organization_Template_example_data.xlsx
+++ b/Organization_Template_example_data.xlsx
@@ -16,8 +16,7 @@
     <sheet name="Contact people" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Interfaces" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Vendor info" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Notes" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Accounts" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Accounts" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
@@ -1075,72 +1074,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16.140625" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>NOTE</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>EBSCO</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Migrated from legacy ERP system on initial load; verify accounts before go-live.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>EBSCO</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Confirm billing contact with vendor before the October renewal cycle.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NORTHWIND</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Contract discontinued; retained for historical order records only.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/Organization_Template_example_data.xlsx
+++ b/Organization_Template_example_data.xlsx
@@ -163,7 +163,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -221,6 +221,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1447,7 +1451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S28"/>
+  <dimension ref="A1:T28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.42578125" customWidth="1" style="8" min="1" max="1"/>
@@ -1462,7 +1466,7 @@
     <col width="17.5703125" customWidth="1" min="13" max="13"/>
     <col width="21.140625" customWidth="1" min="16" max="16"/>
     <col width="25" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="30" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
@@ -1571,10 +1575,15 @@
       </c>
       <c r="R5" s="28" t="inlineStr">
         <is>
-          <t>URL CATEGORY</t>
+          <t>URL NOTE</t>
         </is>
       </c>
       <c r="S5" s="28" t="inlineStr">
+        <is>
+          <t>URL CATEGORIES</t>
+        </is>
+      </c>
+      <c r="T5" s="28" t="inlineStr">
         <is>
           <t>ORG TYPE</t>
         </is>
@@ -1664,10 +1673,15 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Requires vendor portal login credentials</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
+        <is>
+          <t>Support;Sales</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
         <is>
           <t>Subscription Agent</t>
         </is>
@@ -1744,7 +1758,7 @@
           <t>Publisher homepage</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Publisher</t>
         </is>
@@ -1806,7 +1820,7 @@
           <t>friends@springfieldlibrary.org</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Donor</t>
         </is>
@@ -1874,7 +1888,7 @@
         </is>
       </c>
       <c r="P9" s="7" t="n"/>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Museum</t>
         </is>
@@ -1956,7 +1970,12 @@
           <t>https://www.northwindtraders.example</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Domain expired; vendor confirmed inactive</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
         <is>
           <t>Publisher</t>
         </is>
@@ -2028,7 +2047,7 @@
           <t>https://www.acmebinding.example</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Service Provider</t>
         </is>
@@ -2095,7 +2114,7 @@
           <t>https://www.brepols.example</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Publisher</t>
         </is>
@@ -2172,7 +2191,7 @@
           <t>https://www.oclc.example</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Service Provider</t>
         </is>
@@ -2249,7 +2268,7 @@
           <t>https://www.follett.example</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
@@ -2321,7 +2340,7 @@
           <t>https://www.ingramlibrary.example</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
@@ -2393,7 +2412,7 @@
           <t>https://www.baker-taylor.example</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
@@ -2455,7 +2474,7 @@
           <t>friends@riversidelibrary.example</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Donor</t>
         </is>
@@ -2523,7 +2542,7 @@
         </is>
       </c>
       <c r="P18" s="7" t="n"/>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Cultural Institution</t>
         </is>
@@ -2586,7 +2605,7 @@
           <t>info@rilc.example</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Consortium</t>
         </is>
@@ -2721,7 +2740,7 @@
           <t>https://www.metrodigital.example</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Service Provider</t>
         </is>
@@ -2901,7 +2920,7 @@
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>CATEGORY</t>
+          <t>CATEGORIES</t>
         </is>
       </c>
     </row>
@@ -2943,7 +2962,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Billing</t>
+          <t>Billing;Shipping</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3035,7 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>CATEGORY</t>
+          <t>CATEGORIES</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3057,7 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Sales;Support</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3139,7 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>CATEGORY</t>
+          <t>CATEGORIES</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3178,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Sales;Marketing</t>
         </is>
       </c>
     </row>
@@ -3174,22 +3193,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.140625" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="28" t="inlineStr">
+      <c r="A1" s="31" t="inlineStr">
         <is>
           <t>ORG CODE</t>
         </is>
       </c>
-      <c r="B1" s="28" t="inlineStr">
+      <c r="B1" s="31" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
@@ -3201,7 +3220,12 @@
       </c>
       <c r="D1" s="28" t="inlineStr">
         <is>
-          <t>CATEGORY</t>
+          <t>NOTE</t>
+        </is>
+      </c>
+      <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>CATEGORIES</t>
         </is>
       </c>
     </row>
@@ -3223,7 +3247,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Only accessible to registered support accounts</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Support;Technical</t>
         </is>
       </c>
     </row>
@@ -3278,12 +3307,12 @@
           <t>NOTES</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="32" t="inlineStr">
         <is>
           <t>EMAIL</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">PHONE </t>
         </is>
@@ -3295,7 +3324,7 @@
       </c>
       <c r="I1" s="4" t="inlineStr">
         <is>
-          <t>CATEGORY</t>
+          <t>CATEGORIES</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3371,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Renewals</t>
+          <t>Renewals;Support</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3669,7 @@
           <t>ORG CODE</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="32" t="inlineStr">
         <is>
           <t>NAME</t>
         </is>
@@ -3660,12 +3689,12 @@
           <t>DELIVERY METHOD</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="31" t="inlineStr">
         <is>
           <t>USERNAME</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="31" t="inlineStr">
         <is>
           <t>PASSWORD</t>
         </is>

--- a/Organization_Template_example_data.xlsx
+++ b/Organization_Template_example_data.xlsx
@@ -17,6 +17,7 @@
     <sheet name="Interfaces" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Vendor info" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Accounts" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="External note" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
@@ -1444,6 +1445,158 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10.57" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>ORG CODE</t>
+        </is>
+      </c>
+      <c r="B1" s="31" t="inlineStr">
+        <is>
+          <t>NOTE TYPE</t>
+        </is>
+      </c>
+      <c r="C1" s="31" t="inlineStr">
+        <is>
+          <t>NOTE TITLE</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>CONTENTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EBSCO</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Account overview</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Long-standing subscription agent; primary contact is Jan Novak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EBSCO</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Follow-up</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Renewal timing</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Renewal negotiations typically start in Q3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ELSEVIER</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Contract terms</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Reviewing multi-year contract terms currently in effect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NORTHWIND</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Contract discontinued</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Vendor relationship ended 2024; retained for historical records only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>OCLC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Service scope</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Provides cataloging and resource-sharing services across the consortium.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -3267,7 +3420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="20.25" customHeight="1"/>
   <cols>
     <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3299,30 +3452,25 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>TITLE</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
           <t>NOTES</t>
         </is>
       </c>
+      <c r="E1" s="32" t="inlineStr">
+        <is>
+          <t>EMAIL</t>
+        </is>
+      </c>
       <c r="F1" s="32" t="inlineStr">
         <is>
-          <t>EMAIL</t>
-        </is>
-      </c>
-      <c r="G1" s="32" t="inlineStr">
-        <is>
           <t xml:space="preserve">PHONE </t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>CATEGORIES</t>
         </is>
@@ -3346,30 +3494,25 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Account Manager</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
           <t>Prefers email over phone</t>
         </is>
       </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>jnovak@ebsco.com</t>
+        </is>
+      </c>
       <c r="F2" s="10" t="inlineStr">
         <is>
-          <t>jnovak@ebsco.com</t>
-        </is>
-      </c>
-      <c r="G2" s="10" t="inlineStr">
-        <is>
           <t>555-201-0001</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Renewals contact</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Renewals;Support</t>
         </is>
@@ -3391,23 +3534,18 @@
           <t>Mario</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Support Specialist</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>mrossi@ebsco.com</t>
+        </is>
+      </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <t>mrossi@ebsco.com</t>
-        </is>
-      </c>
-      <c r="G3" s="10" t="inlineStr">
-        <is>
           <t>555-201-0002</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Technical support contact</t>
         </is>
@@ -3429,22 +3567,17 @@
           <t>Anke</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Customer Success Manager</t>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>a.devries@elsevier.com</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>a.devries@elsevier.com</t>
+          <t>+31-20-4853700</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
-        <is>
-          <t>+31-20-4853700</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
         <is>
           <t>Primary account contact</t>
         </is>
@@ -3468,25 +3601,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Rights Manager</t>
+          <t>Contract ended 2024, contact for archival questions only</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Contract ended 2024, contact for archival questions only</t>
+          <t>fmacdonald@northwindtraders.example</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>fmacdonald@northwindtraders.example</t>
+          <t>902-555-0111</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
-        <is>
-          <t>902-555-0111</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
         <is>
           <t>Rights and permissions contact</t>
         </is>
@@ -3508,22 +3636,17 @@
           <t>Wei</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Operations Manager</t>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>wchen@acmebinding.example</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>wchen@acmebinding.example</t>
+          <t>614-555-0135</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
-        <is>
-          <t>614-555-0135</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
         <is>
           <t>Scheduling and logistics</t>
         </is>
@@ -3545,22 +3668,17 @@
           <t>Lena</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Sales Representative</t>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>l.peeters@brepols.example</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>l.peeters@brepols.example</t>
+          <t>+32-14-448021</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
-        <is>
-          <t>+32-14-448021</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
         <is>
           <t>Regional sales contact</t>
         </is>
@@ -3582,22 +3700,17 @@
           <t>Diego</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Volunteer Coordinator</t>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>dalvarez@riversidebooks.example</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>dalvarez@riversidebooks.example</t>
+          <t>951-555-0198</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
-        <is>
-          <t>951-555-0198</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
         <is>
           <t>Donations contact</t>
         </is>
@@ -3619,22 +3732,17 @@
           <t>Tam</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Account Executive</t>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>tnguyen@metrodigital.example</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>tnguyen@metrodigital.example</t>
+          <t>916-555-0143</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
-        <is>
-          <t>916-555-0143</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
         <is>
           <t>Primary sales contact</t>
         </is>

--- a/Organization_Template_example_data.xlsx
+++ b/Organization_Template_example_data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-37452" yWindow="10548" windowWidth="21744" windowHeight="11844" tabRatio="731" firstSheet="8" activeTab="8" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1995" yWindow="1800" windowWidth="25050" windowHeight="13140" tabRatio="731" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="How to use this workbook" sheetId="1" state="visible" r:id="rId1"/>
@@ -20,14 +20,14 @@
     <sheet name="External note" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191028" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -107,6 +107,24 @@
       <color theme="0" tint="-0.499984740745262"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF0070C0"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color theme="4"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -164,7 +182,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -180,13 +198,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -197,9 +208,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -218,16 +226,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -609,7 +631,7 @@
   <dimension ref="B2:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12.140625" customWidth="1" min="2" max="2"/>
+    <col width="12.140625" customWidth="1" style="23" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -657,7 +679,7 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>This applies on every sheet, not just Main Org record - e.g. PHONE on the Phones sheet, EMAIL on the Emails sheet, ACCOUNT NAME/ACCOUNT NUMBER/ACCOUNT STATUS on the Accounts sheet. One exception: an interface's USERNAME/PASSWORD (on the Interfaces sheet) aren't colored as mandatory since an interface doesn't need login credentials at all - but if you fill in either one, you must fill in both, or just that login-credentials record is skipped (the interface itself, and the rest of that organization, still build normally).</t>
+          <t>This applies on every sheet, not just Main Org record - e.g. PHONE on the Phones sheet, EMAIL on the Emails sheet, ACCOUNT NAME/ACCOUNT NUMBER/ACCOUNT STATUS on the Accounts sheet. A colored column can also be a 'required if you use this at all' pair rather than a plain single field: an interface's USERNAME/PASSWORD (on the Interfaces sheet) are both colored because if you fill in either one, you must fill in both, or just that login-credentials record is skipped (the interface itself, and the rest of that organization, still build normally). The Interfaces sheet's own NAME column, on the other hand, is intentionally NOT colored - the real FOLIO interface record has no required fields of its own, not even a name.</t>
         </is>
       </c>
     </row>
@@ -682,172 +704,152 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A2:Z11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14.42578125" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="14"/>
+    <col width="14.42578125" customWidth="1" style="23" min="1" max="1"/>
+    <col width="15" customWidth="1" style="23" min="2" max="2"/>
+    <col width="15" customWidth="1" style="23" min="3" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="45" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" s="27" t="inlineStr">
+    <row r="1" ht="45" customHeight="1" s="23"/>
+    <row r="2" ht="45" customHeight="1" s="23">
+      <c r="A2" s="30" t="inlineStr">
+        <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B2" s="26" t="inlineStr">
         <is>
           <t>PAYMENT METHOD</t>
         </is>
       </c>
-      <c r="C1" s="27" t="inlineStr">
+      <c r="C2" s="26" t="inlineStr">
         <is>
           <t>CURRENCIES</t>
         </is>
       </c>
-      <c r="D1" s="27" t="inlineStr">
+      <c r="D2" s="26" t="inlineStr">
         <is>
           <t>CLAIMING INTERVAL</t>
         </is>
       </c>
-      <c r="E1" s="27" t="inlineStr">
+      <c r="E2" s="26" t="inlineStr">
         <is>
           <t>DISCOUNT %</t>
         </is>
       </c>
-      <c r="F1" s="27" t="inlineStr">
+      <c r="F2" s="26" t="inlineStr">
         <is>
           <t>EXP ACTIVATION INTERVAL</t>
         </is>
       </c>
-      <c r="G1" s="27" t="inlineStr">
+      <c r="G2" s="26" t="inlineStr">
         <is>
           <t>EXP INVOICE INTERVAL</t>
         </is>
       </c>
-      <c r="H1" s="27" t="inlineStr">
+      <c r="H2" s="26" t="inlineStr">
         <is>
           <t>EXP RECEIPT INTERVAL</t>
         </is>
       </c>
-      <c r="I1" s="27" t="inlineStr">
+      <c r="I2" s="26" t="inlineStr">
         <is>
           <t>RENEWAL ACTIVATION INTERVAL</t>
         </is>
       </c>
-      <c r="J1" s="27" t="inlineStr">
+      <c r="J2" s="26" t="inlineStr">
         <is>
           <t>SUBSCRIPTION INTERVAL</t>
         </is>
       </c>
-      <c r="K1" s="27" t="inlineStr">
+      <c r="K2" s="26" t="inlineStr">
         <is>
           <t>EXPORT TO ACCOUNTING (Y/)</t>
         </is>
       </c>
-      <c r="L1" s="27" t="inlineStr">
+      <c r="L2" s="26" t="inlineStr">
         <is>
           <t>TAX ID</t>
         </is>
       </c>
-      <c r="M1" s="27" t="inlineStr">
+      <c r="M2" s="26" t="inlineStr">
         <is>
           <t>TAX %</t>
         </is>
       </c>
-      <c r="N1" s="27" t="inlineStr">
+      <c r="N2" s="26" t="inlineStr">
         <is>
           <t>LIABLE FOR VAT (Y/N)</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>EBSCO</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>EFT</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>USD|EUR</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>30</v>
-      </c>
-      <c r="E2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" t="n">
-        <v>14</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H2" t="n">
-        <v>21</v>
-      </c>
-      <c r="I2" t="n">
-        <v>60</v>
-      </c>
-      <c r="J2" t="n">
-        <v>365</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>04-1667882</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Do not edit:</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ELSEVIER</t>
+          <t>GLOBALTECH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Credit Card</t>
+          <t>EFT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
+          <t>USD|EUR</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
+        <v>15</v>
+      </c>
+      <c r="H3" t="n">
+        <v>20</v>
+      </c>
+      <c r="I3" t="n">
+        <v>12</v>
+      </c>
+      <c r="J3" t="n">
+        <v>365</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>12-3456789</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NORTHWIND</t>
+          <t>PRAIRIEBOOKS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -857,15 +859,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CAD</t>
-        </is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>45</v>
       </c>
       <c r="K4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -874,12 +874,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ACMEBIND</t>
+          <t>NORTHSTARLIB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bank Draft</t>
+          <t>Credit Card</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -887,6 +887,12 @@
           <t>USD</t>
         </is>
       </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -894,11 +900,8 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>31-9988776</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>7.5</v>
+          <t>98-7654321</t>
+        </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -909,34 +912,40 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BREPOLS</t>
+          <t>HERITAGEPRES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EFT</t>
+          <t>Bank Draft</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>60</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OCLC</t>
+          <t>SUMMITDATA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -949,26 +958,55 @@
           <t>USD</t>
         </is>
       </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H7" t="n">
+        <v>10</v>
+      </c>
+      <c r="I7" t="n">
+        <v>12</v>
+      </c>
+      <c r="J7" t="n">
+        <v>365</v>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>55-1122334</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>6</v>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FOLLETT</t>
+          <t>LONESTARPUB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Credit Card</t>
+          <t>Physical Check</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -976,12 +1014,10 @@
           <t>USD</t>
         </is>
       </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
       <c r="K8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -990,7 +1026,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>INGRAM</t>
+          <t>BLUEHORIZON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1003,10 +1039,24 @@
           <t>USD</t>
         </is>
       </c>
+      <c r="D9" t="n">
+        <v>45</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>44-9988776</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>5</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1017,12 +1067,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BAKERTAYLOR</t>
+          <t>SILVERLAKE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Physical Check</t>
+          <t>EFT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1030,9 +1080,17 @@
           <t>USD</t>
         </is>
       </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>33-4455667</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1044,7 +1102,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>METRODS</t>
+          <t>TIMBERLINE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1057,18 +1115,24 @@
           <t>USD</t>
         </is>
       </c>
+      <c r="D11" t="n">
+        <v>30</v>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="K3:K1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>$AA$2:$AA$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="N3:N1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1079,217 +1143,156 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13.28515625" customWidth="1" style="20" min="1" max="1"/>
-    <col width="22.140625" customWidth="1" min="2" max="2"/>
-    <col width="20.85546875" customWidth="1" min="3" max="3"/>
-    <col width="36.5703125" customWidth="1" min="4" max="4"/>
-    <col width="24.5703125" customWidth="1" min="5" max="6"/>
-    <col width="25.85546875" customWidth="1" min="7" max="7"/>
-    <col width="18.85546875" customWidth="1" style="15" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="13.28515625" customWidth="1" style="15" min="1" max="1"/>
+    <col width="22.140625" customWidth="1" style="23" min="2" max="2"/>
+    <col width="20.85546875" customWidth="1" style="23" min="3" max="3"/>
+    <col width="36.5703125" customWidth="1" style="23" min="4" max="4"/>
+    <col width="24.5703125" customWidth="1" style="23" min="5" max="6"/>
+    <col width="25.85546875" customWidth="1" style="23" min="7" max="7"/>
+    <col width="18.85546875" customWidth="1" style="10" min="8" max="8"/>
+    <col width="20" customWidth="1" style="23" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" s="24">
-      <c r="A1" s="29" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" s="22" t="inlineStr">
-        <is>
-          <t>ACCOUNT NAME</t>
-        </is>
-      </c>
-      <c r="C1" s="30" t="inlineStr">
-        <is>
-          <t>ACCOUNT NUMBER</t>
-        </is>
-      </c>
-      <c r="D1" s="23" t="inlineStr">
+    <row r="1" customFormat="1" s="27">
+      <c r="B1" s="27" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>ACCOUNT NAME*</t>
+        </is>
+      </c>
+      <c r="C2" s="17" t="inlineStr">
+        <is>
+          <t>ACCOUNT NUMBER*</t>
+        </is>
+      </c>
+      <c r="D2" s="17" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
       </c>
-      <c r="E1" s="23" t="inlineStr">
+      <c r="E2" s="17" t="inlineStr">
         <is>
           <t>ACCOUNTING CODE</t>
         </is>
       </c>
-      <c r="F1" s="23" t="inlineStr">
+      <c r="F2" s="17" t="inlineStr">
         <is>
           <t>PAYMENT METHOD</t>
         </is>
       </c>
-      <c r="G1" s="30" t="inlineStr">
-        <is>
-          <t>ACCOUNT STATUS</t>
-        </is>
-      </c>
-      <c r="H1" s="26" t="inlineStr">
+      <c r="G2" s="17" t="inlineStr">
+        <is>
+          <t>ACCOUNT STATUS*</t>
+        </is>
+      </c>
+      <c r="H2" s="20" t="inlineStr">
         <is>
           <t>LIBRARY EDI CODE</t>
         </is>
       </c>
-      <c r="I1" s="23" t="inlineStr">
+      <c r="I2" s="17" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="19" t="inlineStr">
-        <is>
-          <t>EBSCO</t>
-        </is>
-      </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>EBSCO eBooks</t>
-        </is>
-      </c>
-      <c r="C2" s="25" t="n">
-        <v>12345</v>
-      </c>
-      <c r="D2" s="18" t="inlineStr">
-        <is>
-          <t>eBooks purchased from EBSCO</t>
-        </is>
-      </c>
-      <c r="E2" s="18" t="inlineStr">
-        <is>
-          <t>ACCTSYS-EB</t>
-        </is>
-      </c>
-      <c r="F2" s="18" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>GLOBALTECH</t>
+        </is>
+      </c>
+      <c r="B3" s="25" t="inlineStr">
+        <is>
+          <t>GT eBooks</t>
+        </is>
+      </c>
+      <c r="C3" s="19" t="inlineStr">
+        <is>
+          <t>ACCT-1001</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>eBook purchases</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>EBK-01</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>EFT</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G3" s="25" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H2" s="25" t="n">
-        <v>123</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Renew annually in October</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="19" t="inlineStr">
-        <is>
-          <t>EBSCO</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>EBSCO Databases</t>
-        </is>
-      </c>
-      <c r="C3" s="25" t="n">
-        <v>12346</v>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>databases purchased from EBSCO</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>ACCTSYS-DB</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>EFT</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="19" t="inlineStr">
+        <is>
+          <t>LIB-EDI-01</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Renews annually in June</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>GLOBALTECH</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>GT Databases</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>ACCT-1002</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H3" s="25" t="n">
-        <v>456</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Includes EBSCOhost platform access</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ELSEVIER</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Elsevier Journals</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>55501</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Annual journal subscriptions</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>ACCTSYS-EJ</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Credit Card</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>789</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Multi-year agreement</t>
-        </is>
-      </c>
+      <c r="H4" s="19" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NORTHWIND</t>
+          <t>PRAIRIEBOOKS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Northwind Backlist</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>77012</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Backlist title purchases</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>ACCTSYS-NW</t>
+          <t>PB Print Books</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ACCT-2001</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1299,88 +1302,56 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>321</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Account closed with contract</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ACMEBIND</t>
+          <t>PRAIRIEBOOKS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Binding Services</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>90011</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Ongoing binding and repair services</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>ACCTSYS-AB</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Bank Draft</t>
+          <t>PB AV Media</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ACCT-2002</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Active</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>654</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Invoiced monthly</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BREPOLS</t>
+          <t>NORTHSTARLIB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Brepols Subscriptions</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>44201</v>
+          <t>NSLS Support Plan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ACCT-3001</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Annual journal and series subscriptions</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>ACCTSYS-BR</t>
+          <t>Annual support contract</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>EFT</t>
+          <t>Credit Card</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1388,59 +1359,241 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="H7" t="n">
-        <v>987</v>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Invoiced annually in January</t>
+          <t>Auto-renews</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BAKERTAYLOR</t>
+          <t>NORTHSTARLIB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B&amp;T Standing Orders</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>60312</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Standing order plan for new releases</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>ACCTSYS-BT</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Physical Check</t>
+          <t>NSLS Migration Project</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ACCT-3002</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HERITAGEPRES</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HPG Binding Services</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ACCT-4001</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bank Draft</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H8" t="n">
-        <v>741</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Reviewed quarterly</t>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HERITAGEPRES</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HPG Digitization</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ACCT-4002</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Large-format digitization</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SUMMITDATA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Summit Hosting</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ACCT-5001</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Annual hosting subscription</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>HOST-01</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>EFT</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SUMMITDATA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Summit Analytics Add-on</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ACCT-5002</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LONESTARPUB</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LSP Print Orders</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ACCT-6001</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>REDROCKBIND</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>RRB Repairs</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ACCT-7001</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AMBERWAVE</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>AW Periodicals</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ACCT-8001</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>WILLOWDATA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>WD Metadata Project</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ACCT-9001</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="G3:G1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Active, Inactive, Pending"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1451,144 +1604,184 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A2:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10.57" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="10.5703125" customWidth="1" style="23" min="1" max="1"/>
+    <col width="15" customWidth="1" style="23" min="2" max="2"/>
+    <col width="30" customWidth="1" style="23" min="3" max="3"/>
+    <col width="50" customWidth="1" style="23" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="31" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" s="31" t="inlineStr">
-        <is>
-          <t>NOTE TYPE</t>
-        </is>
-      </c>
-      <c r="C1" s="31" t="inlineStr">
-        <is>
-          <t>NOTE TITLE</t>
-        </is>
-      </c>
-      <c r="D1" s="28" t="inlineStr">
+    <row r="1" ht="15.75" customHeight="1" s="23"/>
+    <row r="2">
+      <c r="A2" s="31" t="inlineStr">
+        <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B2" s="31" t="inlineStr">
+        <is>
+          <t>NOTE TYPE*</t>
+        </is>
+      </c>
+      <c r="C2" s="31" t="inlineStr">
+        <is>
+          <t>NOTE TITLE*</t>
+        </is>
+      </c>
+      <c r="D2" s="31" t="inlineStr">
         <is>
           <t>CONTENTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>EBSCO</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Account overview</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Long-standing subscription agent; primary contact is Jan Novak.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EBSCO</t>
+          <t>GLOBALTECH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Follow-up</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Renewal timing</t>
+          <t>Account overview</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Renewal negotiations typically start in Q3.</t>
+          <t>Long-standing technology vendor; primary contact is Lan Nguyen.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ELSEVIER</t>
+          <t>GLOBALTECH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Follow-up</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Contract terms</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Reviewing multi-year contract terms currently in effect.</t>
+          <t>Renewal timing</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NORTHWIND</t>
+          <t>PRAIRIEBOOKS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Contract discontinued</t>
+          <t>Regional distributor notes</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Vendor relationship ended 2024; retained for historical records only.</t>
+          <t>Serves the Wichita metro area primarily.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OCLC</t>
+          <t>NORTHSTARLIB</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Support agreement</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Three-year support agreement signed 2024.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HERITAGEPRES</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Service scope</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Provides cataloging and resource-sharing services across the consortium.</t>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Specializes in rare manuscripts and large-format materials.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SUMMITDATA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Renewal due soon</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Hosting subscription renews in 60 days; confirm budget approval.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FALCONMEDIA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Contract discontinued</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Vendor relationship ended; retained for historical records only.</t>
         </is>
       </c>
     </row>
@@ -1607,253 +1800,253 @@
   <dimension ref="A1:T28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11.42578125" customWidth="1" style="8" min="1" max="1"/>
-    <col width="25.42578125" customWidth="1" style="8" min="2" max="2"/>
-    <col width="11.5703125" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="16.140625" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="35" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
-    <col width="23.7109375" customWidth="1" min="6" max="6"/>
-    <col width="16.5703125" customWidth="1" min="7" max="7"/>
-    <col width="17.42578125" customWidth="1" min="8" max="8"/>
-    <col width="14.42578125" customWidth="1" min="11" max="11"/>
-    <col width="17.5703125" customWidth="1" min="13" max="13"/>
-    <col width="21.140625" customWidth="1" min="16" max="16"/>
-    <col width="25" customWidth="1" min="17" max="17"/>
-    <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="11.42578125" customWidth="1" style="23" min="1" max="1"/>
+    <col width="25.42578125" customWidth="1" style="23" min="2" max="2"/>
+    <col width="11.5703125" bestFit="1" customWidth="1" style="23" min="3" max="3"/>
+    <col width="16.140625" bestFit="1" customWidth="1" style="23" min="4" max="4"/>
+    <col width="35" bestFit="1" customWidth="1" style="23" min="5" max="5"/>
+    <col width="23.7109375" customWidth="1" style="23" min="6" max="6"/>
+    <col width="16.5703125" customWidth="1" style="23" min="7" max="7"/>
+    <col width="17.42578125" customWidth="1" style="23" min="8" max="8"/>
+    <col width="14.42578125" customWidth="1" style="23" min="11" max="11"/>
+    <col width="17.5703125" customWidth="1" style="23" min="13" max="13"/>
+    <col width="21.140625" customWidth="1" style="23" min="16" max="16"/>
+    <col width="25" customWidth="1" style="23" min="17" max="17"/>
+    <col width="30" customWidth="1" style="23" min="18" max="18"/>
+    <col width="13" customWidth="1" style="23" min="20" max="20"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="B1" s="12" t="inlineStr">
+    <row r="1" ht="18.75" customHeight="1" s="23">
+      <c r="B1" s="33" t="inlineStr">
         <is>
           <t>NOTE: For multivalued fields such as address, alt names, phones, only supply the primary one in this tab. Additional values should be supplied on the other tabs on this sheet</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="18.75" customHeight="1">
-      <c r="B2" s="12" t="n"/>
+    <row r="2" ht="18.75" customHeight="1" s="23">
+      <c r="B2" s="33" t="n"/>
     </row>
     <row r="3">
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>Coloured columns are mandatory.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>ORG NAME</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Columns marked with a red asterisk are mandatory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1" s="23">
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B5" s="30" t="inlineStr">
+        <is>
+          <t>ORG NAME*</t>
+        </is>
+      </c>
+      <c r="C5" s="32" t="inlineStr">
         <is>
           <t>ALT NAME</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="32" t="inlineStr">
         <is>
           <t>Vendor (Yes/No)</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>ORG status (Active/Inactive/Pending)</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="E5" s="32" t="inlineStr">
+        <is>
+          <t>ORG status (Active/Inactive/Pending)*</t>
+        </is>
+      </c>
+      <c r="F5" s="32" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">ADDR1 </t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="32" t="inlineStr">
         <is>
           <t>ADDR2</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="32" t="inlineStr">
         <is>
           <t>CITY</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" s="32" t="inlineStr">
         <is>
           <t>REGION</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K5" s="32" t="inlineStr">
         <is>
           <t>POSTAL CODE</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L5" s="32" t="inlineStr">
         <is>
           <t>COUNTRY</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M5" s="32" t="inlineStr">
         <is>
           <t>PHONE</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N5" s="32" t="inlineStr">
         <is>
           <t>FAX</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O5" s="32" t="inlineStr">
         <is>
           <t>EMAIL</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P5" s="32" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="Q5" s="28" t="inlineStr">
+      <c r="Q5" s="31" t="inlineStr">
         <is>
           <t>URL DESCRIPTION</t>
         </is>
       </c>
-      <c r="R5" s="28" t="inlineStr">
+      <c r="R5" s="31" t="inlineStr">
         <is>
           <t>URL NOTE</t>
         </is>
       </c>
-      <c r="S5" s="28" t="inlineStr">
+      <c r="S5" s="31" t="inlineStr">
         <is>
           <t>URL CATEGORIES</t>
         </is>
       </c>
-      <c r="T5" s="28" t="inlineStr">
+      <c r="T5" s="31" t="inlineStr">
         <is>
           <t>ORG TYPE</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>EBSCO</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>EBSCO Information Services</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>EBSCOhost</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>GLOBALTECH</t>
+        </is>
+      </c>
+      <c r="B6" s="34" t="inlineStr">
+        <is>
+          <t>GlobalTech Solutions Inc.</t>
+        </is>
+      </c>
+      <c r="C6" s="25" t="inlineStr">
+        <is>
+          <t>GT Solutions</t>
+        </is>
+      </c>
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="25" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>Subscription agent and database vendor</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>10 Estes St</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>Ipswich</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>01938</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="F6" s="25" t="inlineStr">
+        <is>
+          <t>Full-service technology vendor with global reach.</t>
+        </is>
+      </c>
+      <c r="G6" s="25" t="inlineStr">
+        <is>
+          <t>100 Innovation Way</t>
+        </is>
+      </c>
+      <c r="H6" s="25" t="inlineStr">
+        <is>
+          <t>Suite 400</t>
+        </is>
+      </c>
+      <c r="I6" s="25" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="J6" s="25" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="K6" s="25" t="inlineStr">
+        <is>
+          <t>73301</t>
+        </is>
+      </c>
+      <c r="L6" s="25" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>978-356-6500</t>
-        </is>
-      </c>
-      <c r="N6" s="5" t="inlineStr">
-        <is>
-          <t>978-356-6600</t>
-        </is>
-      </c>
-      <c r="O6" s="5" t="inlineStr">
-        <is>
-          <t>customerservice@ebsco.com</t>
+      <c r="M6" s="25" t="inlineStr">
+        <is>
+          <t>512-555-0101</t>
+        </is>
+      </c>
+      <c r="N6" s="25" t="n"/>
+      <c r="O6" s="25" t="inlineStr">
+        <is>
+          <t>info@globaltech.example</t>
         </is>
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>https://www.ebsco.com</t>
+          <t>https://www.globaltech.example</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Corporate homepage</t>
+          <t>Corporate site</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Requires vendor portal login credentials</t>
+          <t>Primary marketing site</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>Support;Sales</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>Subscription Agent</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
+          <t>Vendor|Publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1" s="23">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ELSEVIER</t>
+          <t>PRAIRIEBOOKS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Elsevier B.V.</t>
+          <t>Prairie Books &amp; Media</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Elsevier Science</t>
+          <t>Prairie Books</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1868,69 +2061,74 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Journal and ebook publisher</t>
+          <t>Regional book and media distributor.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Radarweg 29</t>
+          <t>55 Prairie Ave</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
-        </is>
-      </c>
-      <c r="K7" s="15" t="inlineStr">
-        <is>
-          <t>1043 NX</t>
+          <t>Wichita</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>KS</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>67202</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>+31-20-4853757</t>
+          <t>316-555-0200</t>
         </is>
       </c>
       <c r="O7" s="7" t="inlineStr">
         <is>
-          <t>journals@elsevier.com</t>
-        </is>
-      </c>
-      <c r="P7" s="14" t="inlineStr">
-        <is>
-          <t>https://www.elsevier.com</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Publisher homepage</t>
+          <t>contact@prairiebooks.example</t>
+        </is>
+      </c>
+      <c r="P7" s="9" t="inlineStr">
+        <is>
+          <t>https://www.prairiebooks.example</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>Publisher</t>
+          <t>Vendor</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FOL-DONOR</t>
+          <t>NORTHSTARLIB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Friends of the Library</t>
+          <t>NorthStar Library Services</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NorthStar</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1940,27 +2138,27 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Local donor organization providing book and material donations</t>
+          <t>Library automation and cataloging services.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>200 Main St</t>
+          <t>12 Polaris Blvd</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Springfield</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>MN</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>62701</t>
+          <t>55401</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1968,61 +2166,76 @@
           <t>USA</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>612-555-0300</t>
+        </is>
+      </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>friends@springfieldlibrary.org</t>
+          <t>help@northstarlib.example</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>https://www.northstarlib.example</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>Donor</t>
+          <t>Service Provider</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SPRINGHIST</t>
+          <t>HERITAGEPRES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Springfield Regional History Museum</t>
+          <t>Heritage Preservation Group</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Heritage Group</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Museum partner providing archival material loans</t>
+          <t>Archival preservation and conservation services.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>45 Heritage Way</t>
+          <t>77 Archive Ln</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Springfield</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>62702</t>
+          <t>02108</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2032,35 +2245,39 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>217-555-0199</t>
+          <t>617-555-0400</t>
         </is>
       </c>
       <c r="O9" s="7" t="inlineStr">
         <is>
-          <t>archives@springfieldhistory.org</t>
-        </is>
-      </c>
-      <c r="P9" s="7" t="n"/>
+          <t>info@heritagepres.example</t>
+        </is>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>https://www.heritagepres.example</t>
+        </is>
+      </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>Museum</t>
+          <t>Material Supplier</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NORTHWIND</t>
+          <t>SUMMITDATA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Northwind Traders Publishing</t>
+          <t>Summit Data Systems</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Northwind Press</t>
+          <t>Summit Data</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2070,84 +2287,79 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Regional academic publisher, contract discontinued</t>
+          <t>Data hosting and discovery platform provider.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>88 Harbor Road</t>
+          <t>900 Ridge Rd</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Floor 4</t>
+          <t>Building C</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Halifax</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="K10" s="15" t="inlineStr">
-        <is>
-          <t>B3J 1A1</t>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="K10" s="10" t="inlineStr">
+        <is>
+          <t>80202</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>902-555-0110</t>
+          <t>303-555-0500</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>orders@northwindtraders.example</t>
+          <t>support@summitdata.example</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>https://www.northwindtraders.example</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>Domain expired; vendor confirmed inactive</t>
+          <t>https://www.summitdata.example</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Publisher</t>
+          <t>Access Provider</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ACMEBIND</t>
+          <t>CEDARARCHIVE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Acme Binding &amp; Preservation Services</t>
+          <t>Cedar Archive Foundation</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2157,64 +2369,44 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Book binding, repair, and preservation services</t>
+          <t>Nonprofit foundation supporting regional archives.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>500 Industrial Blvd</t>
+          <t>4 Cedar Ct</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>OR</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>43004</t>
+          <t>97201</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USA</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>614-555-0134</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>service@acmebinding.example</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>https://www.acmebinding.example</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Service Provider</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BREPOLS</t>
+          <t>LONESTARPUB</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Brepols Publishers</t>
+          <t>Lone Star Publishing</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2229,42 +2421,42 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Belgian academic and humanities publisher</t>
+          <t>Regional publisher of Texas history titles.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Begijnhof 67</t>
+          <t>210 Alamo St</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Turnhout</t>
-        </is>
-      </c>
-      <c r="K12" s="16" t="inlineStr">
-        <is>
-          <t>2300</t>
+          <t>San Antonio</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="K12" s="11" t="inlineStr">
+        <is>
+          <t>78205</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+32-14-448020</t>
+          <t>210-555-0600</t>
         </is>
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>info@brepols.example</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>https://www.brepols.example</t>
+          <t>orders@lonestarpub.example</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -2276,94 +2468,41 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OCLC</t>
+          <t>MOUNTAINVIEW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>OCLC</t>
+          <t>Mountain View Consortium</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Online Computer Library Center</t>
+          <t>MV Consortium</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Global library cooperative providing cataloging and resource-sharing services</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>6565 Kilgour Place</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Dublin</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>OH</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>43017</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>614-764-6000</t>
-        </is>
-      </c>
-      <c r="O13" s="7" t="inlineStr">
-        <is>
-          <t>support@oclc.example</t>
-        </is>
-      </c>
-      <c r="P13" s="7" t="inlineStr">
-        <is>
-          <t>https://www.oclc.example</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Service Provider</t>
-        </is>
-      </c>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="O13" s="7" t="n"/>
+      <c r="P13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FOLLETT</t>
+          <t>BLUEHORIZON</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Follett School Solutions</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Follett</t>
+          <t>Blue Horizon Media</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2378,27 +2517,27 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>K-12 library book and materials vendor</t>
+          <t>Streaming and digital media licensing.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1340 Ridgeview Dr</t>
+          <t>88 Harbor Way</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>McHenry</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>WA</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>60050</t>
+          <t>98101</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2408,39 +2547,39 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>800-621-4272</t>
+          <t>206-555-0700</t>
         </is>
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>orders@follett.example</t>
+          <t>licensing@bluehorizon.example</t>
         </is>
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
-          <t>https://www.follett.example</t>
+          <t>https://www.bluehorizon.example</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>Content Provider</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>INGRAM</t>
+          <t>GREENFIELD</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ingram Library Services</t>
+          <t>Greenfield Historical Society</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2450,64 +2589,19 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Wholesale book distributor and library services provider</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>One Ingram Blvd</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>La Vergne</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>TN</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>37086</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>615-793-5000</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>libraryservices@ingram.example</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>https://www.ingramlibrary.example</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Vendor</t>
+          <t>Local historical society; donor of archival materials.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BAKERTAYLOR</t>
+          <t>REDROCKBIND</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Baker &amp; Taylor</t>
+          <t>Red Rock Bindery</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2522,69 +2616,41 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Book and media distributor for public and academic libraries</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2810 Coliseum Centre Dr</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Charlotte</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="K16" s="15" t="inlineStr">
-        <is>
-          <t>28217</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
+          <t>Book binding and repair services.</t>
+        </is>
+      </c>
+      <c r="K16" s="10" t="n"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>704-998-3100</t>
+          <t>480-555-0800</t>
         </is>
       </c>
       <c r="O16" s="7" t="inlineStr">
         <is>
-          <t>customercare@bakertaylor.example</t>
-        </is>
-      </c>
-      <c r="P16" s="7" t="inlineStr">
-        <is>
-          <t>https://www.baker-taylor.example</t>
-        </is>
-      </c>
+          <t>service@redrockbind.example</t>
+        </is>
+      </c>
+      <c r="P16" s="7" t="n"/>
       <c r="T16" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>Material Supplier</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>RIVFRIENDS</t>
+          <t>SILVERLAKE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Friends of Riverside Library</t>
+          <t>Silverlake Digital</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2594,27 +2660,27 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Volunteer donor group supporting the Riverside public library</t>
+          <t>Digital repository hosting.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>10 Riverside Ave</t>
+          <t>15 Lakeview Dr</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Riverside</t>
+          <t>Madison</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>WI</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>92501</t>
+          <t>53703</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2624,59 +2690,59 @@
       </c>
       <c r="O17" s="7" t="inlineStr">
         <is>
-          <t>friends@riversidelibrary.example</t>
+          <t>support@silverlake.example</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>Donor</t>
+          <t>Access Provider</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CITYARCH</t>
+          <t>AMBERWAVE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>City Archives Preservation Society</t>
+          <t>Amberwave Distribution</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nonprofit partner for archival material preservation and loans</t>
+          <t>Wholesale distributor of periodicals.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>5 Heritage Sq</t>
+          <t>300 Commerce Pkwy</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Riverside</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>92502</t>
+          <t>43215</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2686,30 +2752,26 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>951-555-0110</t>
-        </is>
-      </c>
-      <c r="O18" s="7" t="inlineStr">
-        <is>
-          <t>archives@cityarchives.example</t>
-        </is>
-      </c>
+          <t>614-555-0900</t>
+        </is>
+      </c>
+      <c r="O18" s="7" t="n"/>
       <c r="P18" s="7" t="n"/>
       <c r="T18" t="inlineStr">
         <is>
-          <t>Cultural Institution</t>
+          <t>Vendor</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RILC</t>
+          <t>IRONGATE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Regional Interlibrary Loan Consortium</t>
+          <t>Iron Gate Records Management</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2719,60 +2781,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Defunct regional resource-sharing consortium, retained for historical records</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>400 Consortium Way</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Sacramento</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>95814</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="M19" s="17" t="n"/>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>info@rilc.example</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Consortium</t>
-        </is>
-      </c>
+          <t>Off-site records storage.</t>
+        </is>
+      </c>
+      <c r="M19" s="12" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RIVERSIDE</t>
+          <t>CRYSTALSPR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Riverside Book Exchange</t>
+          <t>Crystal Springs Friends Group</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2782,60 +2809,26 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Used and donated book exchange (status column has a typo/invalid value on purpose)</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>22 Exchange St</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Riverside</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>92503</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>951-555-0199</t>
-        </is>
-      </c>
-      <c r="O20" s="7" t="inlineStr">
-        <is>
-          <t>contact@riversidebooks.example</t>
-        </is>
-      </c>
+          <t>Volunteer group supporting the Crystal Springs branch library.</t>
+        </is>
+      </c>
+      <c r="O20" s="7" t="n"/>
       <c r="P20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>METRODS</t>
+          <t>TIMBERLINE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Metro Digital Solutions</t>
+          <t>Timberline Learning Resources</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2850,27 +2843,27 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Digital archiving and scanning services vendor</t>
+          <t>K-12 and academic learning resource vendor.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>88 Metro Plaza</t>
+          <t>42 Ridgeline Rd</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Boise</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>95815</t>
+          <t>83702</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2878,41 +2871,185 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>916-555-0142</t>
-        </is>
-      </c>
       <c r="O21" s="7" t="inlineStr">
         <is>
-          <t>hello@metrodigital.example</t>
+          <t>sales@timberline.example</t>
         </is>
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
-          <t>https://www.metrodigital.example</t>
+          <t>https://www.timberline.example</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>Service Provider</t>
+          <t>Content Provider</t>
         </is>
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>COASTALARCH</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Coastal Archives Cooperative</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Regional cooperative for shared archival storage.</t>
+        </is>
+      </c>
       <c r="O22" s="7" t="n"/>
       <c r="P22" s="7" t="n"/>
     </row>
     <row r="23">
-      <c r="O23" s="7" t="n"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>WILLOWDATA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Willow Data Services</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Metadata enrichment and data cleanup services.</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>651-555-1000</t>
+        </is>
+      </c>
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t>projects@willowdata.example</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Service Provider</t>
+        </is>
+      </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>STONEBRIDGE</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Stonebridge Consortium</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Multi-library resource-sharing consortium.</t>
+        </is>
+      </c>
       <c r="O24" s="7" t="n"/>
       <c r="P24" s="7" t="n"/>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>FALCONMEDIA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Falcon Media Group</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Media licensing vendor; contract not renewed.</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>10 Falcon Ct</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>85001</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>602-555-1100</t>
+        </is>
+      </c>
       <c r="O25" s="7" t="n"/>
       <c r="P25" s="7" t="n"/>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Content Provider</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="O26" s="7" t="n"/>
@@ -2926,12 +3063,15 @@
       <c r="P28" s="7" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="D6:D1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+  <dataValidations count="3">
+    <dataValidation sqref="D6:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes, No"</formula1>
     </dataValidation>
-    <dataValidation sqref="E6:E1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="E6:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Active, Inactive, Pending"</formula1>
+    </dataValidation>
+    <dataValidation sqref="T6:T1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Access provider,Auction house,Book trade,Consortium,Content provider,Logistics,Material supplier,Membership organization,Private person,Publisher"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2945,74 +3085,109 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A2:C7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="7.7109375" defaultRowHeight="15"/>
   <cols>
-    <col width="15.42578125" customWidth="1" min="1" max="1"/>
-    <col width="11.42578125" customWidth="1" style="8" min="2" max="2"/>
-    <col width="13.28515625" customWidth="1" min="3" max="3"/>
+    <col width="15.42578125" customWidth="1" style="23" min="1" max="1"/>
+    <col width="11.42578125" customWidth="1" style="23" min="2" max="2"/>
+    <col width="13.28515625" customWidth="1" style="23" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" s="13" t="inlineStr">
-        <is>
-          <t>ALT NAME</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
+    <row r="1" ht="15.75" customHeight="1" s="23"/>
+    <row r="2">
+      <c r="A2" s="30" t="inlineStr">
+        <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B2" s="32" t="inlineStr">
+        <is>
+          <t>ALT NAME*</t>
+        </is>
+      </c>
+      <c r="C2" s="32" t="inlineStr">
         <is>
           <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>EBSCO</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>EBSCO Industries</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EBSCO</t>
+          <t>GLOBALTECH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Elton B. Stephens Company</t>
+          <t>GlobalTech</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Historical legal name</t>
+          <t>Marketing name</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NORTHWIND</t>
+          <t>PRAIRIEBOOKS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NW Press</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Common abbreviation</t>
+          <t>PB&amp;M</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NORTHSTARLIB</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NSLS</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Internal acronym</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>HERITAGEPRES</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>HPG</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Acronym</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SUMMITDATA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SDS</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Acronym</t>
         </is>
       </c>
     </row>
@@ -3027,131 +3202,243 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A2:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20.28515625" customWidth="1" min="1" max="1"/>
-    <col width="13.28515625" customWidth="1" min="6" max="6"/>
-    <col width="10.5703125" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="20.28515625" customWidth="1" style="23" min="1" max="1"/>
+    <col width="13.28515625" customWidth="1" style="23" min="6" max="6"/>
+    <col width="10.5703125" bestFit="1" customWidth="1" style="23" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
+    <row r="1" ht="15.75" customHeight="1" s="23"/>
+    <row r="2">
+      <c r="A2" s="30" t="inlineStr">
+        <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B2" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">ADDR1 </t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C2" s="32" t="inlineStr">
         <is>
           <t>ADDR2</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D2" s="32" t="inlineStr">
         <is>
           <t>CITY</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E2" s="32" t="inlineStr">
         <is>
           <t>REGION</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F2" s="32" t="inlineStr">
         <is>
           <t>POSTAL CODE</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G2" s="32" t="inlineStr">
         <is>
           <t>COUNTRY</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H2" s="32" t="inlineStr">
         <is>
           <t>CATEGORIES</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>EBSCO</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>10 Estes St</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Suite 200</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Ipswich</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>01938</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Billing;Shipping</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NORTHWIND</t>
+          <t>GLOBALTECH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12 Industrial Pkwy</t>
+          <t>PO Box 9821</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Dartmouth</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>B2Y 4M6</t>
+          <t>73302</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PRAIRIEBOOKS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>600 Warehouse Dr</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Wichita</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>KS</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>67203</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NORTHSTARLIB</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>12 Polaris Blvd</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Floor 3</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Minneapolis</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>MN</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>55401</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>HERITAGEPRES</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>77 Archive Ln</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Loading Dock B</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>02108</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SUMMITDATA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>900 Ridge Rd</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Building D</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>80202</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>USA</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="H3:H1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Accounts Payable,Administrative,Claims and queries,Customer Service,Licensing,Payments,Receiving orders,Returns,Sales,Shipments,Support"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3162,97 +3449,135 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A2:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16.7109375" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" style="8" min="2" max="2"/>
-    <col width="10.5703125" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="16.7109375" customWidth="1" style="23" min="1" max="1"/>
+    <col width="15" customWidth="1" style="23" min="2" max="2"/>
+    <col width="10.5703125" bestFit="1" customWidth="1" style="23" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" s="13" t="inlineStr">
-        <is>
-          <t>PHONE</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
+    <row r="1" ht="15.75" customHeight="1" s="23"/>
+    <row r="2">
+      <c r="A2" s="30" t="inlineStr">
+        <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B2" s="32" t="inlineStr">
+        <is>
+          <t>PHONE*</t>
+        </is>
+      </c>
+      <c r="C2" s="32" t="inlineStr">
         <is>
           <t>TYPE</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D2" s="32" t="inlineStr">
         <is>
           <t>CATEGORIES</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>EBSCO</t>
-        </is>
-      </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>978-356-7000</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>Sales;Support</t>
-        </is>
-      </c>
-    </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>NORTHWIND</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>902-555-0120</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
+        <is>
+          <t>GLOBALTECH</t>
+        </is>
+      </c>
+      <c r="B3" s="25" t="inlineStr">
+        <is>
+          <t>512-555-0102</t>
+        </is>
+      </c>
+      <c r="C3" s="25" t="inlineStr">
+        <is>
+          <t>Fax</t>
+        </is>
+      </c>
+      <c r="D3" s="25" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>PRAIRIEBOOKS</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>316-555-0201</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>Mobile</t>
         </is>
       </c>
-      <c r="D3" s="5" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>METRODS</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>916-555-0199</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Landline</t>
+      <c r="D4" s="25" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NORTHSTARLIB</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>612-555-0301</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>HERITAGEPRES</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>617-555-0401</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Fax</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SUMMITDATA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>303-555-0501</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Mobile</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+  <dataValidations count="2">
+    <dataValidation sqref="C3:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Office, Mobile, Fax, Other"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D3:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Accounts Payable,Administrative,Claims and queries,Customer Service,Licensing,Payments,Receiving orders,Returns,Sales,Shipments,Support"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3265,77 +3590,124 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A2:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18.140625" customWidth="1" min="1" max="1"/>
-    <col width="27.140625" customWidth="1" style="8" min="2" max="2"/>
-    <col width="27.140625" customWidth="1" min="3" max="3"/>
-    <col width="10.5703125" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="18.140625" customWidth="1" style="23" min="1" max="1"/>
+    <col width="27.140625" customWidth="1" style="23" min="2" max="2"/>
+    <col width="27.140625" customWidth="1" style="23" min="3" max="3"/>
+    <col width="10.5703125" bestFit="1" customWidth="1" style="23" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" s="13" t="inlineStr">
-        <is>
-          <t>EMAIL</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
+    <row r="1" ht="15.75" customHeight="1" s="23"/>
+    <row r="2">
+      <c r="A2" s="30" t="inlineStr">
+        <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B2" s="32" t="inlineStr">
+        <is>
+          <t>EMAIL*</t>
+        </is>
+      </c>
+      <c r="C2" s="32" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D2" s="32" t="inlineStr">
         <is>
           <t>CATEGORIES</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>EBSCO</t>
-        </is>
-      </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>vendorsupport@ebsco.com</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Vendor support</t>
-        </is>
-      </c>
-    </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>EBSCO</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>sales@ebsco.com</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Sales inquiries</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Sales;Marketing</t>
+      <c r="A3" s="25" t="inlineStr">
+        <is>
+          <t>GLOBALTECH</t>
+        </is>
+      </c>
+      <c r="B3" s="25" t="inlineStr">
+        <is>
+          <t>billing@globaltech.example</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>PRAIRIEBOOKS</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>orders@prairiebooks.example</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Order desk</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NORTHSTARLIB</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>sales@northstarlib.example</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>HERITAGEPRES</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>conservation@heritagepres.example</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Conservation team</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SUMMITDATA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>accounts@summitdata.example</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="D3:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Accounts Payable,Administrative,Claims and queries,Customer Service,Licensing,Payments,Receiving orders,Returns,Sales,Shipments,Support"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3346,71 +3718,140 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A2:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18.140625" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="18.140625" customWidth="1" style="23" min="1" max="1"/>
+    <col width="27.140625" customWidth="1" style="23" min="2" max="2"/>
+    <col width="27.140625" customWidth="1" style="23" min="3" max="3"/>
+    <col width="30" bestFit="1" customWidth="1" style="23" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="31" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" s="31" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-      <c r="C1" s="28" t="inlineStr">
+    <row r="1" ht="15.75" customHeight="1" s="23"/>
+    <row r="2">
+      <c r="A2" s="30" t="inlineStr">
+        <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B2" s="31" t="inlineStr">
+        <is>
+          <t>URL*</t>
+        </is>
+      </c>
+      <c r="C2" s="32" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
       </c>
-      <c r="D1" s="28" t="inlineStr">
+      <c r="D2" s="32" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
-      <c r="E1" s="28" t="inlineStr">
+      <c r="E2" s="32" t="inlineStr">
         <is>
           <t>CATEGORIES</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>EBSCO</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>https://support.ebsco.com</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="25" t="inlineStr">
+        <is>
+          <t>GLOBALTECH</t>
+        </is>
+      </c>
+      <c r="B3" s="25" t="inlineStr">
+        <is>
+          <t>https://support.globaltech.example</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>Support portal</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Only accessible to registered support accounts</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Support;Technical</t>
+    </row>
+    <row r="4">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>PRAIRIEBOOKS</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>https://catalog.prairiebooks.example</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Catalog</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Updated weekly</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NORTHSTARLIB</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://status.northstarlib.example</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>System status page</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>HERITAGEPRES</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://www.heritagepres.example/services</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Services overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SUMMITDATA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>https://status.summitdata.example</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Uptime status</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <dataValidations count="1">
+    <dataValidation sqref="E3:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Accounts Payable,Administrative,Claims and queries,Customer Service,Licensing,Payments,Receiving orders,Returns,Sales,Shipments,Support"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -3420,335 +3861,394 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="20.25" customHeight="1"/>
   <cols>
-    <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="11.140625" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
-    <col width="11.7109375" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
-    <col width="6.28515625" customWidth="1" min="4" max="4"/>
-    <col width="7.28515625" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="23.28515625" customWidth="1" style="8" min="6" max="6"/>
-    <col width="14.42578125" customWidth="1" style="8" min="7" max="7"/>
-    <col width="18.28515625" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="10.28515625" bestFit="1" customWidth="1" style="23" min="1" max="1"/>
+    <col width="11.140625" bestFit="1" customWidth="1" style="23" min="2" max="2"/>
+    <col width="11.7109375" bestFit="1" customWidth="1" style="23" min="3" max="3"/>
+    <col width="6.28515625" customWidth="1" style="23" min="4" max="4"/>
+    <col width="7.28515625" bestFit="1" customWidth="1" style="23" min="5" max="5"/>
+    <col width="23.28515625" customWidth="1" style="23" min="6" max="6"/>
+    <col width="14.42578125" customWidth="1" style="23" min="7" max="7"/>
+    <col width="18.28515625" customWidth="1" style="23" min="8" max="8"/>
+    <col width="13" customWidth="1" style="23" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.25" customFormat="1" customHeight="1" s="3">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" s="9" t="inlineStr">
-        <is>
-          <t>LAST NAME</t>
-        </is>
-      </c>
-      <c r="C1" s="9" t="inlineStr">
-        <is>
-          <t>FIRST NAME</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+    <row r="1" ht="20.25" customFormat="1" customHeight="1" s="29">
+      <c r="B1" s="29" t="n"/>
+      <c r="C1" s="29" t="n"/>
+      <c r="D1" s="29" t="n"/>
+      <c r="E1" s="29" t="n"/>
+      <c r="F1" s="29" t="n"/>
+      <c r="G1" s="29" t="n"/>
+    </row>
+    <row r="2" ht="20.25" customHeight="1" s="23">
+      <c r="A2" s="30" t="inlineStr">
+        <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B2" s="30" t="inlineStr">
+        <is>
+          <t>LAST NAME*</t>
+        </is>
+      </c>
+      <c r="C2" s="30" t="inlineStr">
+        <is>
+          <t>FIRST NAME*</t>
+        </is>
+      </c>
+      <c r="D2" s="30" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
-      <c r="E1" s="32" t="inlineStr">
+      <c r="E2" s="24" t="inlineStr">
         <is>
           <t>EMAIL</t>
         </is>
       </c>
-      <c r="F1" s="32" t="inlineStr">
+      <c r="F2" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">PHONE </t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G2" s="30" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>CATEGORIES</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20.25" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>EBSCO</t>
-        </is>
-      </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>Novak</t>
-        </is>
-      </c>
-      <c r="C2" s="10" t="inlineStr">
-        <is>
-          <t>Jan</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>Prefers email over phone</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>jnovak@ebsco.com</t>
-        </is>
-      </c>
-      <c r="F2" s="10" t="inlineStr">
-        <is>
-          <t>555-201-0001</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>Renewals contact</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Renewals;Support</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20.25" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>EBSCO</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>Rossi</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>Mario</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="n"/>
-      <c r="E3" s="10" t="inlineStr">
-        <is>
-          <t>mrossi@ebsco.com</t>
-        </is>
-      </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>555-201-0002</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>Technical support contact</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ELSEVIER</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>de Vries</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Anke</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>a.devries@elsevier.com</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>+31-20-4853700</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Primary account contact</t>
-        </is>
-      </c>
+    <row r="3" ht="20.25" customHeight="1" s="23">
+      <c r="A3" s="25" t="inlineStr">
+        <is>
+          <t>GLOBALTECH</t>
+        </is>
+      </c>
+      <c r="B3" s="25" t="inlineStr">
+        <is>
+          <t>Nguyen</t>
+        </is>
+      </c>
+      <c r="C3" s="25" t="inlineStr">
+        <is>
+          <t>Lan</t>
+        </is>
+      </c>
+      <c r="D3" s="25" t="inlineStr">
+        <is>
+          <t>Primary account manager</t>
+        </is>
+      </c>
+      <c r="E3" s="25" t="inlineStr">
+        <is>
+          <t>lnguyen@globaltech.example</t>
+        </is>
+      </c>
+      <c r="F3" s="25" t="inlineStr">
+        <is>
+          <t>512-555-0111</t>
+        </is>
+      </c>
+      <c r="G3" s="25" t="inlineStr">
+        <is>
+          <t>Direct line, not general support</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sales;Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="23">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>GLOBALTECH</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>Ortiz</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NORTHWIND</t>
+          <t>PRAIRIEBOOKS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MacDonald</t>
+          <t>Whitfield</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fiona</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Contract ended 2024, contact for archival questions only</t>
+          <t>Dana</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>fmacdonald@northwindtraders.example</t>
+          <t>dwhitfield@prairiebooks.example</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>902-555-0111</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Rights and permissions contact</t>
+          <t>316-555-0210</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ACMEBIND</t>
+          <t>PRAIRIEBOOKS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Chen</t>
+          <t>Reyes</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wei</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>wchen@acmebinding.example</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>614-555-0135</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Scheduling and logistics</t>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Handles claims</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Claims</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BREPOLS</t>
+          <t>NORTHSTARLIB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Peeters</t>
+          <t>Park</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lena</t>
+          <t>Ji-woo</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>l.peeters@brepols.example</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>+32-14-448021</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Regional sales contact</t>
+          <t>jpark@northstarlib.example</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RIVERSIDE</t>
+          <t>NORTHSTARLIB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Alvarez</t>
+          <t>Adebayo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Diego</t>
+          <t>Femi</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Escalation contact</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>dalvarez@riversidebooks.example</t>
+          <t>fadebayo@northstarlib.example</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>951-555-0198</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Donations contact</t>
+          <t>612-555-0311</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Support</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>METRODS</t>
+          <t>HERITAGEPRES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nguyen</t>
+          <t>Fitzgerald</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tam</t>
+          <t>Maeve</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>tnguyen@metrodigital.example</t>
+          <t>mfitzgerald@heritagepres.example</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>916-555-0143</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Primary sales contact</t>
+          <t>617-555-0411</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HERITAGEPRES</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Cohen</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Handles large collections</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SUMMITDATA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Alvarez</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Implementation lead</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>salvarez@summitdata.example</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>303-555-0511</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SUMMITDATA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kowalski</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Piotr</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LONESTARPUB</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Guerra</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Isabel</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>iguerra@lonestarpub.example</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AMBERWAVE</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Novak</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Petra</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>pnovak@amberwave.example</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="H3:H1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Accounts Payable,Administrative,Claims and queries,Customer Service,Licensing,Payments,Receiving orders,Returns,Sales,Shipments,Support"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3759,205 +4259,147 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A2:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="14.42578125" customWidth="1" style="8" min="2" max="2"/>
-    <col width="11.85546875" customWidth="1" min="3" max="3"/>
-    <col width="35.7109375" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="6"/>
-    <col width="13.28515625" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="13.140625" customWidth="1" min="8" max="8"/>
+    <col width="10.5703125" bestFit="1" customWidth="1" style="23" min="1" max="1"/>
+    <col width="14.42578125" customWidth="1" style="23" min="2" max="2"/>
+    <col width="11.85546875" customWidth="1" style="23" min="3" max="3"/>
+    <col width="35.7109375" customWidth="1" style="23" min="4" max="4"/>
+    <col width="18" customWidth="1" style="23" min="5" max="6"/>
+    <col width="13.28515625" bestFit="1" customWidth="1" style="23" min="7" max="7"/>
+    <col width="13.140625" customWidth="1" style="23" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" s="32" t="inlineStr">
+    <row r="1" ht="15.75" customHeight="1" s="23"/>
+    <row r="2" ht="30" customHeight="1" s="23">
+      <c r="A2" s="30" t="inlineStr">
+        <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B2" s="24" t="inlineStr">
         <is>
           <t>NAME</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C2" s="32" t="inlineStr">
         <is>
           <t>TYPE</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D2" s="32" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="E1" s="28" t="inlineStr">
+      <c r="E2" s="31" t="inlineStr">
         <is>
           <t>DELIVERY METHOD</t>
         </is>
       </c>
-      <c r="F1" s="31" t="inlineStr">
-        <is>
-          <t>USERNAME</t>
-        </is>
-      </c>
-      <c r="G1" s="31" t="inlineStr">
-        <is>
-          <t>PASSWORD</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="F2" s="31" t="inlineStr">
+        <is>
+          <t>USERNAME*</t>
+        </is>
+      </c>
+      <c r="G2" s="31" t="inlineStr">
+        <is>
+          <t>PASSWORD*</t>
+        </is>
+      </c>
+      <c r="H2" s="32" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I2" s="32" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>EBSCO</t>
-        </is>
-      </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>EBSCO Admin</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>https://eadmin.ebscohost.com/eadmin</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="25" t="inlineStr">
+        <is>
+          <t>GLOBALTECH</t>
+        </is>
+      </c>
+      <c r="B3" s="25" t="inlineStr">
+        <is>
+          <t>GT Admin Portal</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Admin|Orders</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>https://admin.globaltech.example</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>Online</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>ebsco_admin_user</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>p@ssw0rd123</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>Administrative interface</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Used by acquisitions staff</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>EBSCO</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>EBSCONET</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Orders</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>https://www.ebsconet.com</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Online</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>ebsco_order_user</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>order_pass456</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>Ordering and claiming interface</t>
+      <c r="F3" s="25" t="inlineStr">
+        <is>
+          <t>gt_admin</t>
+        </is>
+      </c>
+      <c r="G3" s="25" t="inlineStr">
+        <is>
+          <t>s3cur3-pass</t>
+        </is>
+      </c>
+      <c r="H3" s="25" t="inlineStr">
+        <is>
+          <t>Ignored by the schema (no home for it)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Primary interface for order management</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ELSEVIER</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ScienceDirect Admin</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>https://www.sciencedirect.com/admin</t>
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>GLOBALTECH</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>GT Reports Feed</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
+        <is>
+          <t>https://reports.globaltech.example</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Online</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>elsevier_admin</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>sdAdminPass1</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Platform administration</t>
-        </is>
-      </c>
+          <t>FTP</t>
+        </is>
+      </c>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NORTHWIND</t>
+          <t>PRAIRIEBOOKS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Northwind Ordering Portal</t>
+          <t>PB Order System</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3967,125 +4409,331 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://orders.northwindtraders.example</t>
+          <t>https://orders.prairiebooks.example</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FTP</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>nw_user</t>
+          <t>pb_orders</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>nwPass789</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Legacy ordering portal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Decommissioned, kept for reference</t>
+          <t>pb-pass-1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OCLC</t>
+          <t>PRAIRIEBOOKS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WorldShare Admin</t>
+          <t>PB Invoices</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>https://worldshare.oclc.example/admin</t>
+          <t>Invoices</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Online</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>oclc_admin</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>wsAdminPass1</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Cataloging platform administration</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>METRODS</t>
+          <t>NORTHSTARLIB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Metro Scan Portal</t>
+          <t>NSLS Cataloging Tool</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://cat.northstarlib.example</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ns_admin</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ns-pass-2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Requires VPN</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NORTHSTARLIB</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NSLS Reports</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Reports</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HERITAGEPRES</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HPG Order Portal</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>https://portal.metrodigital.example</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://orders.heritagepres.example</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>hpg_user</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>hpg-pass-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HERITAGEPRES</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HPG EDI Feed</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Legacy EDI connection, rarely used</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SUMMITDATA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Summit API</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Admin|End user</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://api.summitdata.example</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>summit_api</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>summit-pass-4</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>OAuth2 credentials rotate every 90 days</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SUMMITDATA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Summit Billing Portal</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Invoices</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://billing.summitdata.example</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LONESTARPUB</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LSP Order Line</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Orders</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>metro_user</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>metroPass1</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Job submission portal</t>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SILVERLAKE</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Silverlake Admin</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://admin.silverlake.example</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>sl_admin</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>sl-pass-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>WILLOWDATA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Willow Project Portal</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>End user</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://portal.willowdata.example</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Online</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="C3:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Admin, End user, Reports, Orders, Invoices, Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="E3:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Online, FTP, Email, Other"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Organization_Template_example_data.xlsx
+++ b/Organization_Template_example_data.xlsx
@@ -1797,7 +1797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T28"/>
+  <dimension ref="A1:AD28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.42578125" customWidth="1" style="23" min="1" max="1"/>
@@ -1851,85 +1851,135 @@
       </c>
       <c r="D5" s="32" t="inlineStr">
         <is>
+          <t>ALT NAME DESCRIPTION</t>
+        </is>
+      </c>
+      <c r="E5" s="32" t="inlineStr">
+        <is>
           <t>Vendor (Yes/No)</t>
         </is>
       </c>
-      <c r="E5" s="32" t="inlineStr">
+      <c r="F5" s="32" t="inlineStr">
         <is>
           <t>ORG status (Active/Inactive/Pending)*</t>
         </is>
       </c>
-      <c r="F5" s="32" t="inlineStr">
+      <c r="G5" s="32" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="G5" s="32" t="inlineStr">
+      <c r="H5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">ADDR1 </t>
         </is>
       </c>
-      <c r="H5" s="32" t="inlineStr">
+      <c r="I5" s="32" t="inlineStr">
         <is>
           <t>ADDR2</t>
         </is>
       </c>
-      <c r="I5" s="32" t="inlineStr">
+      <c r="J5" s="32" t="inlineStr">
         <is>
           <t>CITY</t>
         </is>
       </c>
-      <c r="J5" s="32" t="inlineStr">
+      <c r="K5" s="32" t="inlineStr">
         <is>
           <t>REGION</t>
         </is>
       </c>
-      <c r="K5" s="32" t="inlineStr">
+      <c r="L5" s="32" t="inlineStr">
         <is>
           <t>POSTAL CODE</t>
         </is>
       </c>
-      <c r="L5" s="32" t="inlineStr">
+      <c r="M5" s="32" t="inlineStr">
         <is>
           <t>COUNTRY</t>
         </is>
       </c>
-      <c r="M5" s="32" t="inlineStr">
+      <c r="N5" s="32" t="inlineStr">
+        <is>
+          <t>ADDR LANGUAGE</t>
+        </is>
+      </c>
+      <c r="O5" s="32" t="inlineStr">
+        <is>
+          <t>ADDR CATEGORIES</t>
+        </is>
+      </c>
+      <c r="P5" s="32" t="inlineStr">
         <is>
           <t>PHONE</t>
         </is>
       </c>
-      <c r="N5" s="32" t="inlineStr">
+      <c r="Q5" s="32" t="inlineStr">
+        <is>
+          <t>PHONE TYPE</t>
+        </is>
+      </c>
+      <c r="R5" s="32" t="inlineStr">
+        <is>
+          <t>PHONE LANGUAGE</t>
+        </is>
+      </c>
+      <c r="S5" s="32" t="inlineStr">
+        <is>
+          <t>PHONE CATEGORIES</t>
+        </is>
+      </c>
+      <c r="T5" s="32" t="inlineStr">
         <is>
           <t>FAX</t>
         </is>
       </c>
-      <c r="O5" s="32" t="inlineStr">
+      <c r="U5" s="32" t="inlineStr">
         <is>
           <t>EMAIL</t>
         </is>
       </c>
-      <c r="P5" s="32" t="inlineStr">
+      <c r="V5" s="32" t="inlineStr">
+        <is>
+          <t>EMAIL DESCRIPTION</t>
+        </is>
+      </c>
+      <c r="W5" s="32" t="inlineStr">
+        <is>
+          <t>EMAIL LANGUAGE</t>
+        </is>
+      </c>
+      <c r="X5" s="32" t="inlineStr">
+        <is>
+          <t>EMAIL CATEGORIES</t>
+        </is>
+      </c>
+      <c r="Y5" s="32" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="Q5" s="31" t="inlineStr">
+      <c r="Z5" s="31" t="inlineStr">
         <is>
           <t>URL DESCRIPTION</t>
         </is>
       </c>
-      <c r="R5" s="31" t="inlineStr">
+      <c r="AA5" s="32" t="inlineStr">
+        <is>
+          <t>URL LANGUAGE</t>
+        </is>
+      </c>
+      <c r="AB5" s="31" t="inlineStr">
         <is>
           <t>URL NOTE</t>
         </is>
       </c>
-      <c r="S5" s="31" t="inlineStr">
+      <c r="AC5" s="31" t="inlineStr">
         <is>
           <t>URL CATEGORIES</t>
         </is>
       </c>
-      <c r="T5" s="31" t="inlineStr">
+      <c r="AD5" s="31" t="inlineStr">
         <is>
           <t>ORG TYPE</t>
         </is>
@@ -1951,83 +2001,118 @@
           <t>GT Solutions</t>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Common shorthand used internally</t>
+        </is>
+      </c>
+      <c r="E6" s="25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E6" s="25" t="inlineStr">
+      <c r="F6" s="25" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="F6" s="25" t="inlineStr">
+      <c r="G6" s="25" t="inlineStr">
         <is>
           <t>Full-service technology vendor with global reach.</t>
         </is>
       </c>
-      <c r="G6" s="25" t="inlineStr">
+      <c r="H6" s="25" t="inlineStr">
         <is>
           <t>100 Innovation Way</t>
         </is>
       </c>
-      <c r="H6" s="25" t="inlineStr">
+      <c r="I6" s="25" t="inlineStr">
         <is>
           <t>Suite 400</t>
         </is>
       </c>
-      <c r="I6" s="25" t="inlineStr">
+      <c r="J6" s="25" t="inlineStr">
         <is>
           <t>Austin</t>
         </is>
       </c>
-      <c r="J6" s="25" t="inlineStr">
+      <c r="K6" s="25" t="inlineStr">
         <is>
           <t>TX</t>
         </is>
       </c>
-      <c r="K6" s="25" t="inlineStr">
+      <c r="L6" s="25" t="inlineStr">
         <is>
           <t>73301</t>
         </is>
       </c>
-      <c r="L6" s="25" t="inlineStr">
+      <c r="M6" s="25" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="M6" s="25" t="inlineStr">
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Billing;Shipping</t>
+        </is>
+      </c>
+      <c r="P6" s="25" t="inlineStr">
         <is>
           <t>512-555-0101</t>
         </is>
       </c>
-      <c r="N6" s="25" t="n"/>
-      <c r="O6" s="25" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Sales;Support</t>
+        </is>
+      </c>
+      <c r="T6" s="25" t="n"/>
+      <c r="U6" s="25" t="inlineStr">
         <is>
           <t>info@globaltech.example</t>
         </is>
       </c>
-      <c r="P6" s="6" t="inlineStr">
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>General inquiries</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>eng</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Support;Sales</t>
+        </is>
+      </c>
+      <c r="Y6" s="6" t="inlineStr">
         <is>
           <t>https://www.globaltech.example</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>Corporate site</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>Primary marketing site</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>Vendor|Publisher</t>
         </is>
@@ -2051,60 +2136,80 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>Short form</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Regional book and media distributor.</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>55 Prairie Ave</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Wichita</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>KS</t>
         </is>
       </c>
-      <c r="K7" s="10" t="inlineStr">
+      <c r="L7" s="10" t="inlineStr">
         <is>
           <t>67202</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Shipping</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>316-555-0200</t>
         </is>
       </c>
-      <c r="O7" s="7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="U7" s="7" t="inlineStr">
         <is>
           <t>contact@prairiebooks.example</t>
         </is>
       </c>
-      <c r="P7" s="9" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>eng</t>
+        </is>
+      </c>
+      <c r="Y7" s="9" t="inlineStr">
         <is>
           <t>https://www.prairiebooks.example</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
@@ -2126,62 +2231,87 @@
           <t>NorthStar</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Library automation and cataloging services.</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>12 Polaris Blvd</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Minneapolis</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>MN</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>55401</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>612-555-0300</t>
         </is>
       </c>
-      <c r="O8" s="7" t="inlineStr">
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="U8" s="7" t="inlineStr">
         <is>
           <t>help@northstarlib.example</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Support desk</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>eng</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>https://www.northstarlib.example</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>Service Provider</t>
         </is>
@@ -2203,62 +2333,77 @@
           <t>Heritage Group</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Archival preservation and conservation services.</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>77 Archive Ln</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>02108</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Shipping</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
         <is>
           <t>617-555-0400</t>
         </is>
       </c>
-      <c r="O9" s="7" t="inlineStr">
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="U9" s="7" t="inlineStr">
         <is>
           <t>info@heritagepres.example</t>
         </is>
       </c>
-      <c r="P9" s="7" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>eng</t>
+        </is>
+      </c>
+      <c r="Y9" s="7" t="inlineStr">
         <is>
           <t>https://www.heritagepres.example</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>Material Supplier</t>
         </is>
@@ -2280,67 +2425,97 @@
           <t>Summit Data</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Data hosting and discovery platform provider.</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>900 Ridge Rd</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Building C</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Denver</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="K10" s="10" t="inlineStr">
+      <c r="L10" s="10" t="inlineStr">
         <is>
           <t>80202</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
         <is>
           <t>303-555-0500</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
         <is>
           <t>support@summitdata.example</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>24/7 support</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>eng</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
         <is>
           <t>https://www.summitdata.example</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>Access Provider</t>
         </is>
@@ -2357,42 +2532,42 @@
           <t>Cedar Archive Foundation</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Nonprofit foundation supporting regional archives.</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>4 Cedar Ct</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Portland</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>97201</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
@@ -2409,57 +2584,62 @@
           <t>Lone Star Publishing</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Regional publisher of Texas history titles.</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>210 Alamo St</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>San Antonio</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>TX</t>
         </is>
       </c>
-      <c r="K12" s="11" t="inlineStr">
+      <c r="L12" s="11" t="inlineStr">
         <is>
           <t>78205</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>210-555-0600</t>
         </is>
       </c>
-      <c r="O12" s="7" t="inlineStr">
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="U12" s="7" t="inlineStr">
         <is>
           <t>orders@lonestarpub.example</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>Publisher</t>
         </is>
@@ -2481,18 +2661,18 @@
           <t>MV Consortium</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="O13" s="7" t="n"/>
-      <c r="P13" s="7" t="n"/>
+      <c r="U13" s="7" t="n"/>
+      <c r="Y13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2505,62 +2685,77 @@
           <t>Blue Horizon Media</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Streaming and digital media licensing.</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>88 Harbor Way</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Seattle</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>WA</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>98101</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Licensing</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
         <is>
           <t>206-555-0700</t>
         </is>
       </c>
-      <c r="O14" s="7" t="inlineStr">
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="U14" s="7" t="inlineStr">
         <is>
           <t>licensing@bluehorizon.example</t>
         </is>
       </c>
-      <c r="P14" s="7" t="inlineStr">
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Licensing</t>
+        </is>
+      </c>
+      <c r="Y14" s="7" t="inlineStr">
         <is>
           <t>https://www.bluehorizon.example</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>Content Provider</t>
         </is>
@@ -2577,17 +2772,17 @@
           <t>Greenfield Historical Society</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Local historical society; donor of archival materials.</t>
         </is>
@@ -2604,34 +2799,39 @@
           <t>Red Rock Bindery</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Book binding and repair services.</t>
         </is>
       </c>
-      <c r="K16" s="10" t="n"/>
-      <c r="M16" t="inlineStr">
+      <c r="L16" s="10" t="n"/>
+      <c r="P16" t="inlineStr">
         <is>
           <t>480-555-0800</t>
         </is>
       </c>
-      <c r="O16" s="7" t="inlineStr">
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="U16" s="7" t="inlineStr">
         <is>
           <t>service@redrockbind.example</t>
         </is>
       </c>
-      <c r="P16" s="7" t="n"/>
-      <c r="T16" t="inlineStr">
+      <c r="Y16" s="7" t="n"/>
+      <c r="AD16" t="inlineStr">
         <is>
           <t>Material Supplier</t>
         </is>
@@ -2648,52 +2848,57 @@
           <t>Silverlake Digital</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Digital repository hosting.</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>15 Lakeview Dr</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Madison</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>WI</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>53703</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="O17" s="7" t="inlineStr">
+      <c r="U17" s="7" t="inlineStr">
         <is>
           <t>support@silverlake.example</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
         <is>
           <t>Access Provider</t>
         </is>
@@ -2710,54 +2915,64 @@
           <t>Amberwave Distribution</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Wholesale distributor of periodicals.</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>300 Commerce Pkwy</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Columbus</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>OH</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>43215</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Shipping</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
         <is>
           <t>614-555-0900</t>
         </is>
       </c>
-      <c r="O18" s="7" t="n"/>
-      <c r="P18" s="7" t="n"/>
-      <c r="T18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="U18" s="7" t="n"/>
+      <c r="Y18" s="7" t="n"/>
+      <c r="AD18" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
@@ -2774,22 +2989,22 @@
           <t>Iron Gate Records Management</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Off-site records storage.</t>
         </is>
       </c>
-      <c r="M19" s="12" t="n"/>
+      <c r="P19" s="12" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2802,23 +3017,23 @@
           <t>Crystal Springs Friends Group</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Volunteer group supporting the Crystal Springs branch library.</t>
         </is>
       </c>
-      <c r="O20" s="7" t="n"/>
-      <c r="P20" s="7" t="n"/>
+      <c r="U20" s="7" t="n"/>
+      <c r="Y20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2831,57 +3046,62 @@
           <t>Timberline Learning Resources</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>K-12 and academic learning resource vendor.</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>42 Ridgeline Rd</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Boise</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>83702</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="O21" s="7" t="inlineStr">
+      <c r="U21" s="7" t="inlineStr">
         <is>
           <t>sales@timberline.example</t>
         </is>
       </c>
-      <c r="P21" s="7" t="inlineStr">
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="Y21" s="7" t="inlineStr">
         <is>
           <t>https://www.timberline.example</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="AD21" t="inlineStr">
         <is>
           <t>Content Provider</t>
         </is>
@@ -2898,23 +3118,23 @@
           <t>Coastal Archives Cooperative</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Regional cooperative for shared archival storage.</t>
         </is>
       </c>
-      <c r="O22" s="7" t="n"/>
-      <c r="P22" s="7" t="n"/>
+      <c r="U22" s="7" t="n"/>
+      <c r="Y22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2927,32 +3147,37 @@
           <t>Willow Data Services</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>Metadata enrichment and data cleanup services.</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>651-555-1000</t>
         </is>
       </c>
-      <c r="O23" s="7" t="inlineStr">
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="U23" s="7" t="inlineStr">
         <is>
           <t>projects@willowdata.example</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="AD23" t="inlineStr">
         <is>
           <t>Service Provider</t>
         </is>
@@ -2969,23 +3194,23 @@
           <t>Stonebridge Consortium</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>Multi-library resource-sharing consortium.</t>
         </is>
       </c>
-      <c r="O24" s="7" t="n"/>
-      <c r="P24" s="7" t="n"/>
+      <c r="U24" s="7" t="n"/>
+      <c r="Y24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2998,80 +3223,97 @@
           <t>Falcon Media Group</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Media licensing vendor; contract not renewed.</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>10 Falcon Ct</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Phoenix</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>85001</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>602-555-1100</t>
         </is>
       </c>
-      <c r="O25" s="7" t="n"/>
-      <c r="P25" s="7" t="n"/>
-      <c r="T25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="U25" s="7" t="n"/>
+      <c r="Y25" s="7" t="n"/>
+      <c r="AD25" t="inlineStr">
         <is>
           <t>Content Provider</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="O26" s="7" t="n"/>
-      <c r="P26" s="7" t="n"/>
+      <c r="U26" s="7" t="n"/>
+      <c r="Y26" s="7" t="n"/>
     </row>
     <row r="27">
-      <c r="O27" s="7" t="n"/>
-      <c r="P27" s="7" t="n"/>
+      <c r="U27" s="7" t="n"/>
+      <c r="Y27" s="7" t="n"/>
     </row>
     <row r="28">
-      <c r="P28" s="7" t="n"/>
+      <c r="Y28" s="7" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation sqref="D6:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="7">
+    <dataValidation sqref="E6:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes, No"</formula1>
     </dataValidation>
-    <dataValidation sqref="E6:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6:F1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Active, Inactive, Pending"</formula1>
     </dataValidation>
-    <dataValidation sqref="T6:T1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AD6:AD1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Access provider,Auction house,Book trade,Consortium,Content provider,Logistics,Material supplier,Membership organization,Private person,Publisher"</formula1>
+    </dataValidation>
+    <dataValidation sqref="O6:O1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Accounts Payable,Administrative,Claims and queries,Customer Service,Licensing,Payments,Receiving orders,Returns,Sales,Shipments,Support"</formula1>
+    </dataValidation>
+    <dataValidation sqref="Q6:Q1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Office, Mobile, Fax, Other"</formula1>
+    </dataValidation>
+    <dataValidation sqref="S6:S1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Accounts Payable,Administrative,Claims and queries,Customer Service,Licensing,Payments,Receiving orders,Returns,Sales,Shipments,Support"</formula1>
+    </dataValidation>
+    <dataValidation sqref="X6:X1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Accounts Payable,Administrative,Claims and queries,Customer Service,Licensing,Payments,Receiving orders,Returns,Sales,Shipments,Support"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3590,7 +3832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:D7"/>
+  <dimension ref="A2:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.140625" customWidth="1" style="23" min="1" max="1"/>
@@ -3618,6 +3860,11 @@
       </c>
       <c r="D2" s="32" t="inlineStr">
         <is>
+          <t>LANGUAGE</t>
+        </is>
+      </c>
+      <c r="E2" s="32" t="inlineStr">
+        <is>
           <t>CATEGORIES</t>
         </is>
       </c>
@@ -3662,7 +3909,7 @@
           <t>sales@northstarlib.example</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
@@ -3684,7 +3931,7 @@
           <t>Conservation team</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
@@ -3704,7 +3951,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="D3:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E3:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Accounts Payable,Administrative,Claims and queries,Customer Service,Licensing,Payments,Receiving orders,Returns,Sales,Shipments,Support"</formula1>
     </dataValidation>
   </dataValidations>
